--- a/data/trans_dic/IP7_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP7_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general regular o mala</t>
+          <t>Menores con salud general regular o mala (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 11,69</t>
+          <t>1,37; 12,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 11,47</t>
+          <t>1,02; 13,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 16,88</t>
+          <t>3,21; 16,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 37,69</t>
+          <t>4,44; 39,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,05</t>
+          <t>0,0; 7,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 11,49</t>
+          <t>1,36; 11,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 13,94</t>
+          <t>2,72; 13,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 12,29</t>
+          <t>2,23; 12,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,6</t>
+          <t>1,25; 7,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,18</t>
+          <t>2,15; 9,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 12,53</t>
+          <t>4,29; 13,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 21,5</t>
+          <t>4,63; 24,47</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,9</t>
+          <t>0,57; 4,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,86</t>
+          <t>1,23; 7,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,57</t>
+          <t>0,56; 6,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,73</t>
+          <t>0,72; 6,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 8,1</t>
+          <t>1,78; 7,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 8,2</t>
+          <t>1,75; 8,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,12</t>
+          <t>1,23; 7,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,1</t>
+          <t>0,41; 5,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,32</t>
+          <t>1,53; 5,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,08</t>
+          <t>1,89; 6,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,48</t>
+          <t>1,21; 5,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,63</t>
+          <t>1,03; 4,37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 5,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,52</t>
+          <t>0,0; 5,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,03</t>
+          <t>0,86; 7,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,01</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,75</t>
+          <t>0,0; 6,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,75</t>
+          <t>0,45; 4,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,16</t>
+          <t>1,12; 8,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 9,24</t>
+          <t>1,49; 9,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,57</t>
+          <t>1,15; 10,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 8,65</t>
+          <t>0,86; 9,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,85</t>
+          <t>0,85; 8,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,74</t>
+          <t>0,0; 10,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,48</t>
+          <t>0,44; 4,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,46</t>
+          <t>0,96; 5,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,83</t>
+          <t>1,8; 7,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,49</t>
+          <t>0,81; 6,95</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,51</t>
+          <t>1,47; 12,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,07</t>
+          <t>0,0; 7,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 17,07</t>
+          <t>3,08; 16,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 14,64</t>
+          <t>1,73; 14,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,36</t>
+          <t>0,0; 7,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 11,4</t>
+          <t>2,98; 11,69</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 7,96</t>
+          <t>1,45; 8,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,46</t>
+          <t>0,0; 6,16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,57</t>
+          <t>0,0; 6,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,62</t>
+          <t>0,0; 6,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,41</t>
+          <t>0,0; 6,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,18</t>
+          <t>0,0; 7,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,54</t>
+          <t>0,0; 7,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,18</t>
+          <t>0,0; 6,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 8,82</t>
+          <t>0,64; 8,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,72</t>
+          <t>0,53; 4,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,23</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,95</t>
+          <t>0,66; 5,67</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,85</t>
+          <t>0,47; 4,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,39</t>
+          <t>0,62; 5,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,01</t>
+          <t>0,96; 5,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,45</t>
+          <t>0,44; 4,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,67</t>
+          <t>0,48; 4,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,2</t>
+          <t>1,54; 7,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,35</t>
+          <t>0,75; 3,62</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,27</t>
+          <t>0,69; 2,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,87</t>
+          <t>0,49; 3,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,31</t>
+          <t>1,57; 5,46</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,46</t>
+          <t>0,39; 3,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,87</t>
+          <t>0,93; 5,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,48</t>
+          <t>2,07; 7,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,16</t>
+          <t>0,45; 3,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,56</t>
+          <t>1,64; 4,78</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,57</t>
+          <t>1,04; 3,66</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,8</t>
+          <t>0,18; 1,78</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,74</t>
+          <t>1,04; 2,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,49</t>
+          <t>1,42; 3,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,97</t>
+          <t>1,21; 2,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,15</t>
+          <t>1,88; 6,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,9</t>
+          <t>2,61; 4,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,56</t>
+          <t>1,7; 3,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,12</t>
+          <t>1,38; 3,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,6</t>
+          <t>1,61; 3,68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,4</t>
+          <t>1,96; 3,36</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,16</t>
+          <t>1,83; 3,14</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,62</t>
+          <t>1,44; 2,67</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,29</t>
+          <t>2,03; 4,42</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con salud general regular o mala (tasa de respuesta: 99,72%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2718</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2854</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4845</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9937</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1383</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3024</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4168</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4547</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9014</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>14484</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>719; 6423</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>577; 7411</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1816; 9385</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3252; 28741</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4221</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>861; 7328</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1737; 8789</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1773; 9868</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1405; 8402</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2581; 10984</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5166; 15805</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>7075; 37346</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3242</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2338</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3591</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4472</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4648</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3733</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2211</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6312</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7890</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6071</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5802</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>583; 4920</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1284; 7747</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>581; 7015</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>921; 8239</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1926; 8460</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1944; 9976</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1355; 8727</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>529; 6792</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3199; 11329</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>4080; 13379</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2579; 11694</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2642; 11166</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1854</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1527</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1527</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3963</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3709</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>608; 4954</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3252</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4619</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>619; 6572</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5603</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4684</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2859</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2860</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2770</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2823</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1463</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2770</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3921</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6055</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4323</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>869; 6945</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1143; 7353</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>809; 7511</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>677; 7309</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3658</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>693; 6800</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 8181</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>671; 6614</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1525; 8425</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2844; 11133</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1206; 10305</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3341</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>5444</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3341</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1148</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>616; 5407</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2650</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1380; 7335</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>810; 6852</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3044</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2584; 10137</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1319; 7434</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4634</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1670</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1914</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2338</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3447</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3908</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3182</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3283</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4333</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3527</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3898</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>362; 4677</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>609; 5187</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4997</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4724</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>676; 5799</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2693</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>3378</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5745</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>4711</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>4533</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>4021</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>8438</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4075</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>647; 5922</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4262</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>772; 7069</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1296; 7809</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>641; 6170</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>694; 6569</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2401; 11728</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1980; 9520</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1946; 8458</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>1366; 8557</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>4393; 15319</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4242</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>6800</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>905</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>9160</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>6992</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2339</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1753</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>623; 5609</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1537; 8460</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3238</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4388</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>3395; 12134</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>776; 6362</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4370</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5424</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>5265; 15381</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>3488; 12293</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>590; 5957</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0; 6063</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>11645</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>16619</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>13398</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>21144</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>25414</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>18726</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>15499</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>18669</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>37059</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>35346</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>28897</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>39813</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>7110; 18445</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10097; 23497</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>8476; 20490</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>12519; 43018</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>18773; 34175</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>12736; 26443</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>10206; 22578</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>12240; 28009</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>27470; 47114</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>26744; 45809</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>20816; 38452</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>29035; 63150</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>